--- a/French Ligue 1/Raw/16_17.xlsx
+++ b/French Ligue 1/Raw/16_17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Desktop\Value_Betting_Projekt\French Ligue 1\Raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6000B8B7-C50F-4081-94F3-D4BC33905D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3181595-A60E-4EDC-A052-656F5D93BAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="175">
   <si>
     <t>Dato</t>
   </si>
@@ -42770,6 +42770,9 @@
       <c r="A328" t="s">
         <v>161</v>
       </c>
+      <c r="B328" t="s">
+        <v>46</v>
+      </c>
       <c r="C328" t="s">
         <v>44</v>
       </c>
@@ -42832,6 +42835,9 @@
       </c>
       <c r="W328" t="s">
         <v>63</v>
+      </c>
+      <c r="X328">
+        <v>0</v>
       </c>
       <c r="Y328">
         <v>4</v>
